--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,7 +523,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>页签:system=系统说明(FG13 FGR-UX-050);其余页签由 FG2-FW-05 扩</t>
+          <t>页签:system=系统说明(FG13 FGR-UX-050);固件 / 反应页签的条目由 fg.TbFirmwareKind / fg.TbReaction 生成(FG2-FW-05),不在本表</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>codex.signal.uplink,codex.signal.uplink_port,codex.signal.raw</t>
+          <t>codex.signal.uplink,codex.signal.uplink_port,codex.signal.raw,codex.firmware.library</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -965,6 +965,47 @@
       </c>
       <c r="I13" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>codex.firmware.library</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>codex.firmware.library.title</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>codex.firmware.library.body</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>codex.firmware.library.hint</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>codex.signal.core_firmware,codex.signal.raw</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>firmware.library.first_open</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1008,6 +1008,47 @@
         <v>110</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>codex.firmware.restore</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>codex.firmware.restore.title</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>codex.firmware.restore.body</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>codex.firmware.restore.hint</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>codex.firmware.library,codex.signal.raw</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>firmware.restore.first_done</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1049,6 +1049,47 @@
         <v>120</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>codex.build.grid</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>codex.build.grid.title</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>codex.build.grid.body</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>codex.build.grid.hint</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>codex.signal.coverage</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>build.mode.first_open,build.relocate.first,build.demolish.first_batch</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1090,6 +1090,47 @@
         <v>130</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>codex.build.construction</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>codex.build.construction.title</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>codex.build.construction.body</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>codex.build.construction.hint</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>codex.build.grid</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>build.ghost.first,build.ghost.first_waiting,build.queue.first_open</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>140</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,6 +1131,47 @@
         <v>140</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>codex.logistics.belt</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>codex.logistics.belt.title</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>codex.logistics.belt.body</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>codex.logistics.belt.hint</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>codex.build.grid,codex.build.construction</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>logistics.belt.first_placed,logistics.belt.first_blocked,logistics.port.first_connected</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1172,6 +1172,47 @@
         <v>150</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>codex.logistics.splitter</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>codex.logistics.splitter.title</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>codex.logistics.splitter.body</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>codex.logistics.splitter.hint</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>codex.logistics.belt,codex.build.grid</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>logistics.splitter.first_placed,logistics.merger.first_placed,logistics.underground.first_placed</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>160</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1213,6 +1213,88 @@
         <v>160</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>codex.logistics.pipe</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>codex.logistics.pipe.title</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>codex.logistics.pipe.body</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>codex.logistics.pipe.hint</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>codex.logistics.fluid,codex.logistics.belt,codex.build.grid</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>logistics.pipe.first_placed</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>codex.logistics.fluid</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>codex.logistics.fluid.title</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>codex.logistics.fluid.body</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>codex.logistics.fluid.hint</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>codex.logistics.pipe</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>logistics.pipe.first_panel_open,logistics.pipe.first_fluid_conflict,logistics.pipe.first_no_supply</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>180</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1295,6 +1295,47 @@
         <v>180</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>codex.logistics.power</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>codex.logistics.power.title</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>codex.logistics.power.body</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>codex.logistics.power.hint</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>codex.build.grid,codex.build.construction</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>power.pole.first_placed,power.first_brownout,power.panel.first_open,power.first_split</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>190</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1336,6 +1336,47 @@
         <v>190</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>codex.build.planning</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>codex.build.planning.title</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>codex.build.planning.body</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>codex.build.planning.hint</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>codex.build.grid,codex.build.construction,codex.logistics.belt</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>build.plan.first_copy,build.plan.first_paste,build.plan.first_undo,build.plan.first_upgrade,build.plan.first_eyedropper,build.plan.first_copy_settings,build.plan.first_layout_saved,build.plan.library_first_open</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1377,6 +1377,47 @@
         <v>200</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>codex.logistics.diagnosis</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>codex.logistics.diagnosis.title</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>codex.logistics.diagnosis.body</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>codex.logistics.diagnosis.hint</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>codex.logistics.belt,codex.logistics.power,codex.logistics.fluid</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>logistics.overlay.first_open,logistics.diagnosis.first_open,logistics.port.first_output_blocked</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>210</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1418,6 +1418,47 @@
         <v>210</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>codex.economy.items</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>codex.economy.items.title</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>codex.economy.items.body</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>codex.economy.items.hint</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>codex.logistics.belt,codex.logistics.fluid</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>economy.items.first_open</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>220</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1459,6 +1459,88 @@
         <v>220</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>codex.economy.gathering</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>codex.economy.gathering.title</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>codex.economy.gathering.body</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>codex.economy.gathering.hint</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>codex.economy.processing,codex.economy.items</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>economy.gathering.first_placed</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>codex.economy.processing</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>codex.economy.processing.title</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>codex.economy.processing.body</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>codex.economy.processing.hint</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>codex.economy.gathering,codex.economy.items</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>economy.processing.first_placed</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>240</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,6 +1541,88 @@
         <v>240</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>codex.economy.manufacturing</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>codex.economy.manufacturing.title</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>codex.economy.manufacturing.body</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>codex.economy.manufacturing.hint</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>codex.economy.processing,codex.economy.assembly,codex.economy.items</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>economy.manufacturing.first_placed</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>codex.economy.assembly</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>codex.economy.assembly.title</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>codex.economy.assembly.body</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>codex.economy.assembly.hint</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>codex.economy.manufacturing,codex.economy.items</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>economy.assembly.first_line_machine</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>260</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,6 +1623,47 @@
         <v>260</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>codex.economy.energy</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>codex.economy.energy.title</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>codex.economy.energy.body</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>codex.economy.energy.hint</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>codex.logistics.power,codex.economy.processing</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>energy.first_built,energy.first_fuel_out</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>260</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1664,6 +1664,47 @@
         <v>260</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>codex.build.building</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>codex.build.building.title</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>codex.build.building.body</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>codex.build.building.hint</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>codex.build.construction,codex.build.planning,codex.economy.manufacturing</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>building.panel_first_open,building.first_upgrade,building.first_damaged</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>270</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1705,6 +1705,47 @@
         <v>270</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>codex.economy.rules</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>codex.economy.rules.title</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>codex.economy.rules.body</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>codex.economy.rules.hint</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>codex.economy.items,codex.build.building</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>rules.panel_first_open,rules.first_created</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>280</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1746,6 +1746,47 @@
         <v>280</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>codex.economy.roster</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>codex.economy.roster.title</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>codex.economy.roster.body</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>codex.economy.roster.hint</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>codex.economy.rules,codex.build.building</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>roster.panel_first_open,roster.first_role_change,roster.first_rename</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>290</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1787,6 +1787,47 @@
         <v>290</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>codex.economy.stats</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>codex.economy.stats.title</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>codex.economy.stats.body</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>codex.economy.stats.hint</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>codex.economy.items,codex.build.building</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>stats.production_first_open,planner.first_plan,stats.first_pin,stats.first_deficit</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>300</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1828,6 +1828,47 @@
         <v>300</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>codex.economy.away</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>codex.economy.away.title</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>codex.economy.away.body</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>codex.economy.away.hint</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>codex.economy.stats,codex.economy.roster</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>away.report_first_open,away.first_auto_open,alarm.first_factory_jam,alarm.first_machine_wounded</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>310</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1869,6 +1869,47 @@
         <v>310</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>codex.economy.softlock</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>codex.economy.softlock.title</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>codex.economy.softlock.body</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>codex.economy.softlock.hint</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>codex.economy.gathering,codex.economy.processing,codex.economy.away</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>economy.softlock.first_print,economy.softlock.first_core_scrap,economy.softlock.first_loop_stall,economy.softlock.first_unreachable,economy.production.first_byproduct_blocked</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>320</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1910,6 +1910,47 @@
         <v>320</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>codex.signal.override_array</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>codex.signal.override_array.title</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>codex.signal.override_array.body</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>codex.signal.override_array.hint</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>codex.signal.core_firmware,codex.build.building</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>override_array.first_built,override_array.first_offline</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>285</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1951,6 +1951,88 @@
         <v>285</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>codex.research.lab</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>codex.research.lab.title</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>codex.research.lab.body</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>codex.research.lab.hint</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>codex.research.tree,codex.build.building</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>research.lab_first_built</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>codex.research.tree</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>codex.research.tree.title</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>codex.research.tree.body</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>codex.research.tree.hint</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>codex.research.lab</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>research.tree_first_open</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>291</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2033,6 +2033,47 @@
         <v>291</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>codex.research.analysis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>codex.research.analysis.title</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>codex.research.analysis.body</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>codex.research.analysis.hint</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>codex.research.lab,codex.economy.items</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>analysis.first_enemy_item</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>292</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2074,6 +2074,47 @@
         <v>292</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>codex.research.range</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>codex.research.range.title</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>codex.research.range.body</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>codex.research.range.hint</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>codex.research.lab,codex.research.analysis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>range.first_built,range.first_open</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>293</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2115,6 +2115,88 @@
         <v>293</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>codex.research.fusion</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>codex.research.fusion.title</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>codex.research.fusion.body</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>codex.research.fusion.hint</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>codex.research.recipe_book,codex.research.lab,codex.research.analysis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>fusion.first_built,fusion.first_open</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>codex.research.recipe_book</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>codex.research.recipe_book.title</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>codex.research.recipe_book.body</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>codex.research.recipe_book.hint</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>codex.research.fusion,codex.research.lab</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>fusion.first_clue,fusion.first_discovery,fusion.first_recipe_book</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>295</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2197,6 +2197,252 @@
         <v>295</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>codex.intel.listening_post</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>codex.intel.listening_post.title</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>codex.intel.listening_post.body</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>codex.intel.listening_post.hint</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>codex.intel.raid_forecast,codex.intel.counter_preview,codex.intel.boss_weakness,codex.intel.weather,codex.intel.fleet_fragment,codex.research.tree</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>intel.first_built,intel.first_open</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>codex.intel.raid_forecast</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>codex.intel.raid_forecast.title</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>codex.intel.raid_forecast.body</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>codex.intel.raid_forecast.hint</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>codex.intel.listening_post</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>intel.first_open,intel.first_intel</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>codex.intel.counter_preview</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>codex.intel.counter_preview.title</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>codex.intel.counter_preview.body</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>codex.intel.counter_preview.hint</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>codex.intel.listening_post</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>intel.first_open,intel.first_intel</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>codex.intel.boss_weakness</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>codex.intel.boss_weakness.title</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>codex.intel.boss_weakness.body</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>codex.intel.boss_weakness.hint</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>codex.intel.listening_post</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>intel.first_open,intel.first_intel</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>codex.intel.weather</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>codex.intel.weather.title</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>codex.intel.weather.body</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>codex.intel.weather.hint</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>codex.intel.listening_post</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>intel.first_open,intel.first_intel</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>codex.intel.fleet_fragment</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>codex.intel.fleet_fragment.title</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>codex.intel.fleet_fragment.body</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>codex.intel.fleet_fragment.hint</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>codex.intel.listening_post</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>intel.first_open,intel.first_intel</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>335</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2443,6 +2443,47 @@
         <v>335</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>codex.blackbox.gallery</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>codex.blackbox.gallery.title</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>codex.blackbox.gallery.body</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>codex.blackbox.gallery.hint</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>codex.research.lab</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>blackbox.first_recovered,blackbox.first_built,blackbox.first_open</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>340</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,6 +2484,47 @@
         <v>340</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>codex.defense.turret</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>codex.defense.turret.title</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>codex.defense.turret.body</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>codex.defense.turret.hint</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>codex.build.building,codex.signal.uplink</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>turret.first_built,turret.first_open</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2525,6 +2525,129 @@
         <v>296</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>codex.defense.barrier</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>codex.defense.barrier.title</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>codex.defense.barrier.body</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>codex.defense.barrier.hint</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>codex.defense.turret,codex.build.building</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>defense.barrier_first_built,defense.gate_first_built</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>codex.defense.shield</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>codex.defense.shield.title</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>codex.defense.shield.body</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>codex.defense.shield.hint</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>codex.defense.turret,codex.defense.barrier</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>defense.shield_first_built,defense.shield_first_overload</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>codex.defense.trap</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>codex.defense.trap.title</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>codex.defense.trap.body</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>codex.defense.trap.hint</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>codex.defense.turret,codex.defense.barrier</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>defense.trap_first_built,defense.trap_first_supply_short</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>299</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2648,6 +2648,47 @@
         <v>299</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>codex.defense.repair_drone</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>codex.defense.repair_drone.title</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>codex.defense.repair_drone.body</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>codex.defense.repair_drone.hint</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>codex.defense.turret,codex.defense.barrier,codex.build.building</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>defense.repair_drone_first_built,defense.repair_drone_first_repair</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>300</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2689,6 +2689,47 @@
         <v>300</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>codex.raid.director</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>codex.raid.director.title</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>codex.raid.director.body</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>codex.raid.director.hint</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>codex.intel.raid_forecast,codex.signal.exposure,codex.defense.turret</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>raid.first_planned,raid.first_warning</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>312</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2730,6 +2730,47 @@
         <v>312</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>codex.raid.siege</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>codex.raid.siege.title</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>codex.raid.siege.body</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>codex.raid.siege.hint</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>codex.raid.director,codex.defense.barrier,codex.defense.turret</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>siege.first_unfold,siege.first_breach</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>313</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2771,6 +2771,88 @@
         <v>313</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>codex.raid.hud</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>codex.raid.hud.title</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>codex.raid.hud.body</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>codex.raid.hud.hint</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>codex.raid.director,codex.raid.siege,codex.defense.overview</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>raid.hud_first_active,raid.first_spectate,raid.first_auto_pause</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>codex.defense.overview</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>codex.defense.overview.title</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>codex.defense.overview.body</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>codex.defense.overview.hint</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>codex.defense.turret,codex.raid.siege,codex.raid.hud</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>defense.overview_first_open,defense.first_weak_point</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>315</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2853,6 +2853,47 @@
         <v>315</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>codex.raid.away</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>codex.raid.away.title</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>codex.raid.away.body</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>codex.raid.away.hint</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>codex.raid.hud,codex.raid.director</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>raid.away_first_alert,raid.away_first_choice</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>316</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2894,6 +2894,47 @@
         <v>316</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>codex.raid.result</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>codex.raid.result.title</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>codex.raid.result.body</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>codex.raid.result.hint</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>codex.raid.siege,codex.raid.director,codex.raid.away</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>raid.first_result,raid.result_first_open</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>317</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2935,6 +2935,47 @@
         <v>317</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>codex.raid.difficulty</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>codex.raid.difficulty.title</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>codex.raid.difficulty.body</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>codex.raid.difficulty.hint</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>codex.raid.director,codex.raid.siege</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>difficulty.first_open,difficulty.first_changed</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>318</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2976,6 +2976,47 @@
         <v>318</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>codex.logistics.leak</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>codex.logistics.leak.title</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>codex.logistics.leak.body</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>codex.logistics.leak.hint</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>codex.logistics.pipe,codex.logistics.fluid,codex.raid.siege</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>logistics.leak.first,logistics.leak.first_react</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>215</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3017,6 +3017,47 @@
         <v>215</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>codex.env.daynight</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>codex.env.daynight.title</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>codex.env.daynight.body</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>codex.env.daynight.hint</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>codex.economy.energy,codex.raid.director</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>env.first_night,env.calendar_first_open</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>330</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3058,6 +3058,47 @@
         <v>330</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>codex.env.silent_night</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>codex.env.silent_night.title</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>codex.env.silent_night.body</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>codex.env.silent_night.hint</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>codex.env.daynight,codex.raid.director</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>env.first_silent_warning,env.first_silent_night,env.first_storm_debris</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>331</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3099,6 +3099,88 @@
         <v>331</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>codex.env.weather</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>codex.env.weather.title</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>codex.env.weather.body</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>codex.env.weather.hint</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>codex.env.daynight,codex.env.roof,codex.intel.weather</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>env.first_weather_warning,env.first_weather,env.first_pipe_frozen</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>codex.env.roof</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>codex.env.roof.title</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>codex.env.roof.body</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>codex.env.roof.hint</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>codex.env.weather</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>env.first_roof,env.first_weather</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>333</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3181,6 +3181,129 @@
         <v>333</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>codex.env.pollution</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>codex.env.pollution.title</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>codex.env.pollution.body</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>codex.env.pollution.hint</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>codex.env.purification,codex.env.returned_area,codex.env.weather</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>env.first_pollution_seen,env.first_repollution</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>codex.env.purification</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>codex.env.purification.title</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>codex.env.purification.body</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>codex.env.purification.hint</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>codex.env.pollution,codex.env.returned_area</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>env.first_purifier,env.first_purified</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>codex.env.returned_area</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>codex.env.returned_area.title</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>codex.env.returned_area.body</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>codex.env.returned_area.hint</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>codex.env.purification,codex.env.pollution</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>env.first_purified,env.first_return_milestone</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>336</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3304,6 +3304,88 @@
         <v>336</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>codex.env.exploration</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>codex.env.exploration.title</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>codex.env.exploration.body</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>codex.env.exploration.hint</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>codex.env.hazard,codex.env.returned_area</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>env.first_fog_blocked,env.first_relic_found,env.first_relic_recovered</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>codex.env.hazard</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>codex.env.hazard.title</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>codex.env.hazard.body</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>codex.env.hazard.hint</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>codex.env.exploration</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>env.first_hazard_seen</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>338</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3386,6 +3386,88 @@
         <v>338</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>codex.world.territories</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>codex.world.territories.title</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>codex.world.territories.body</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>codex.world.territories.hint</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>codex.env.hazard,codex.world.interior</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>world.first_territory_entered,world.first_poi_found</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>codex.world.interior</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>codex.world.interior.title</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>codex.world.interior.body</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>codex.world.interior.hint</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>codex.world.territories</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>world.first_interior_entered,world.first_entrance_blocked</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>340</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3468,6 +3468,47 @@
         <v>340</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>codex.world.control</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>codex.world.control.title</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>codex.world.control.body</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>codex.world.control.hint</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>codex.world.territories</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>world.first_outpost_destroyed,world.first_territory_pacified,world.first_territory_reclaimed</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>341</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2693,7 +2693,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>codex.raid.director</t>
+          <t>codex.expedition.drop</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2703,38 +2703,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>codex.raid.director.title</t>
+          <t>codex.expedition.drop.title</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>codex.raid.director.body</t>
+          <t>codex.expedition.drop.body</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>codex.raid.director.hint</t>
+          <t>codex.expedition.drop.hint</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>codex.intel.raid_forecast,codex.signal.exposure,codex.defense.turret</t>
+          <t>codex.economy.manufacturing,codex.build.building</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>raid.first_planned,raid.first_warning</t>
+          <t>drop.first_station_built,drop.first_panel_open,drop.first_antiair_rejected</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>codex.raid.siege</t>
+          <t>codex.raid.director</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2744,38 +2744,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>codex.raid.siege.title</t>
+          <t>codex.raid.director.title</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>codex.raid.siege.body</t>
+          <t>codex.raid.director.body</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>codex.raid.siege.hint</t>
+          <t>codex.raid.director.hint</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>codex.raid.director,codex.defense.barrier,codex.defense.turret</t>
+          <t>codex.intel.raid_forecast,codex.signal.exposure,codex.defense.turret</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>siege.first_unfold,siege.first_breach</t>
+          <t>raid.first_planned,raid.first_warning</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>codex.raid.hud</t>
+          <t>codex.raid.siege</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2785,38 +2785,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>codex.raid.hud.title</t>
+          <t>codex.raid.siege.title</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>codex.raid.hud.body</t>
+          <t>codex.raid.siege.body</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>codex.raid.hud.hint</t>
+          <t>codex.raid.siege.hint</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>codex.raid.director,codex.raid.siege,codex.defense.overview</t>
+          <t>codex.raid.director,codex.defense.barrier,codex.defense.turret</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>raid.hud_first_active,raid.first_spectate,raid.first_auto_pause</t>
+          <t>siege.first_unfold,siege.first_breach</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>codex.defense.overview</t>
+          <t>codex.raid.hud</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2826,38 +2826,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>codex.defense.overview.title</t>
+          <t>codex.raid.hud.title</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>codex.defense.overview.body</t>
+          <t>codex.raid.hud.body</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>codex.defense.overview.hint</t>
+          <t>codex.raid.hud.hint</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>codex.defense.turret,codex.raid.siege,codex.raid.hud</t>
+          <t>codex.raid.director,codex.raid.siege,codex.defense.overview</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>defense.overview_first_open,defense.first_weak_point</t>
+          <t>raid.hud_first_active,raid.first_spectate,raid.first_auto_pause</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>codex.raid.away</t>
+          <t>codex.defense.overview</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2867,38 +2867,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>codex.raid.away.title</t>
+          <t>codex.defense.overview.title</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>codex.raid.away.body</t>
+          <t>codex.defense.overview.body</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>codex.raid.away.hint</t>
+          <t>codex.defense.overview.hint</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>codex.raid.hud,codex.raid.director</t>
+          <t>codex.defense.turret,codex.raid.siege,codex.raid.hud</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>raid.away_first_alert,raid.away_first_choice</t>
+          <t>defense.overview_first_open,defense.first_weak_point</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>codex.raid.result</t>
+          <t>codex.raid.away</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2908,38 +2908,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>codex.raid.result.title</t>
+          <t>codex.raid.away.title</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>codex.raid.result.body</t>
+          <t>codex.raid.away.body</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>codex.raid.result.hint</t>
+          <t>codex.raid.away.hint</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>codex.raid.siege,codex.raid.director,codex.raid.away</t>
+          <t>codex.raid.hud,codex.raid.director</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>raid.first_result,raid.result_first_open</t>
+          <t>raid.away_first_alert,raid.away_first_choice</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>codex.raid.difficulty</t>
+          <t>codex.raid.result</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2949,38 +2949,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>codex.raid.difficulty.title</t>
+          <t>codex.raid.result.title</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>codex.raid.difficulty.body</t>
+          <t>codex.raid.result.body</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>codex.raid.difficulty.hint</t>
+          <t>codex.raid.result.hint</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>codex.raid.director,codex.raid.siege</t>
+          <t>codex.raid.siege,codex.raid.director,codex.raid.away</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>difficulty.first_open,difficulty.first_changed</t>
+          <t>raid.first_result,raid.result_first_open</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>codex.logistics.leak</t>
+          <t>codex.raid.difficulty</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2990,38 +2990,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>codex.logistics.leak.title</t>
+          <t>codex.raid.difficulty.title</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>codex.logistics.leak.body</t>
+          <t>codex.raid.difficulty.body</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>codex.logistics.leak.hint</t>
+          <t>codex.raid.difficulty.hint</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>codex.logistics.pipe,codex.logistics.fluid,codex.raid.siege</t>
+          <t>codex.raid.director,codex.raid.siege</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>logistics.leak.first,logistics.leak.first_react</t>
+          <t>difficulty.first_open,difficulty.first_changed</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>215</v>
+        <v>318</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>codex.env.daynight</t>
+          <t>codex.logistics.leak</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3031,38 +3031,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>codex.env.daynight.title</t>
+          <t>codex.logistics.leak.title</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>codex.env.daynight.body</t>
+          <t>codex.logistics.leak.body</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>codex.env.daynight.hint</t>
+          <t>codex.logistics.leak.hint</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>codex.economy.energy,codex.raid.director</t>
+          <t>codex.logistics.pipe,codex.logistics.fluid,codex.raid.siege</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>env.first_night,env.calendar_first_open</t>
+          <t>logistics.leak.first,logistics.leak.first_react</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>330</v>
+        <v>215</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>codex.env.silent_night</t>
+          <t>codex.env.daynight</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3072,38 +3072,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>codex.env.silent_night.title</t>
+          <t>codex.env.daynight.title</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>codex.env.silent_night.body</t>
+          <t>codex.env.daynight.body</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>codex.env.silent_night.hint</t>
+          <t>codex.env.daynight.hint</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>codex.env.daynight,codex.raid.director</t>
+          <t>codex.economy.energy,codex.raid.director</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>env.first_silent_warning,env.first_silent_night,env.first_storm_debris</t>
+          <t>env.first_night,env.calendar_first_open</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>codex.env.weather</t>
+          <t>codex.env.silent_night</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3113,38 +3113,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>codex.env.weather.title</t>
+          <t>codex.env.silent_night.title</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>codex.env.weather.body</t>
+          <t>codex.env.silent_night.body</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>codex.env.weather.hint</t>
+          <t>codex.env.silent_night.hint</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>codex.env.daynight,codex.env.roof,codex.intel.weather</t>
+          <t>codex.env.daynight,codex.raid.director</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>env.first_weather_warning,env.first_weather,env.first_pipe_frozen</t>
+          <t>env.first_silent_warning,env.first_silent_night,env.first_storm_debris</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>codex.env.roof</t>
+          <t>codex.env.weather</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3154,38 +3154,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>codex.env.roof.title</t>
+          <t>codex.env.weather.title</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>codex.env.roof.body</t>
+          <t>codex.env.weather.body</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>codex.env.roof.hint</t>
+          <t>codex.env.weather.hint</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>codex.env.weather</t>
+          <t>codex.env.daynight,codex.env.roof,codex.intel.weather</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>env.first_roof,env.first_weather</t>
+          <t>env.first_weather_warning,env.first_weather,env.first_pipe_frozen</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>codex.env.pollution</t>
+          <t>codex.env.roof</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3195,38 +3195,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>codex.env.pollution.title</t>
+          <t>codex.env.roof.title</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>codex.env.pollution.body</t>
+          <t>codex.env.roof.body</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>codex.env.pollution.hint</t>
+          <t>codex.env.roof.hint</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>codex.env.purification,codex.env.returned_area,codex.env.weather</t>
+          <t>codex.env.weather</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>env.first_pollution_seen,env.first_repollution</t>
+          <t>env.first_roof,env.first_weather</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>codex.env.purification</t>
+          <t>codex.env.pollution</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3236,38 +3236,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>codex.env.purification.title</t>
+          <t>codex.env.pollution.title</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>codex.env.purification.body</t>
+          <t>codex.env.pollution.body</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>codex.env.purification.hint</t>
+          <t>codex.env.pollution.hint</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>codex.env.pollution,codex.env.returned_area</t>
+          <t>codex.env.purification,codex.env.returned_area,codex.env.weather</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>env.first_purifier,env.first_purified</t>
+          <t>env.first_pollution_seen,env.first_repollution</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>codex.env.returned_area</t>
+          <t>codex.env.purification</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3277,38 +3277,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>codex.env.returned_area.title</t>
+          <t>codex.env.purification.title</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>codex.env.returned_area.body</t>
+          <t>codex.env.purification.body</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>codex.env.returned_area.hint</t>
+          <t>codex.env.purification.hint</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>codex.env.purification,codex.env.pollution</t>
+          <t>codex.env.pollution,codex.env.returned_area</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>env.first_purified,env.first_return_milestone</t>
+          <t>env.first_purifier,env.first_purified</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>codex.env.exploration</t>
+          <t>codex.env.returned_area</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3318,38 +3318,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>codex.env.exploration.title</t>
+          <t>codex.env.returned_area.title</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>codex.env.exploration.body</t>
+          <t>codex.env.returned_area.body</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>codex.env.exploration.hint</t>
+          <t>codex.env.returned_area.hint</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>codex.env.hazard,codex.env.returned_area</t>
+          <t>codex.env.purification,codex.env.pollution</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>env.first_fog_blocked,env.first_relic_found,env.first_relic_recovered</t>
+          <t>env.first_purified,env.first_return_milestone</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>codex.env.hazard</t>
+          <t>codex.env.exploration</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3359,38 +3359,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>codex.env.hazard.title</t>
+          <t>codex.env.exploration.title</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>codex.env.hazard.body</t>
+          <t>codex.env.exploration.body</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>codex.env.hazard.hint</t>
+          <t>codex.env.exploration.hint</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>codex.env.exploration</t>
+          <t>codex.env.hazard,codex.env.returned_area</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>env.first_hazard_seen</t>
+          <t>env.first_fog_blocked,env.first_relic_found,env.first_relic_recovered</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>codex.world.territories</t>
+          <t>codex.env.hazard</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3400,38 +3400,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>codex.world.territories.title</t>
+          <t>codex.env.hazard.title</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>codex.world.territories.body</t>
+          <t>codex.env.hazard.body</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>codex.world.territories.hint</t>
+          <t>codex.env.hazard.hint</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>codex.env.hazard,codex.world.interior</t>
+          <t>codex.env.exploration</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>world.first_territory_entered,world.first_poi_found</t>
+          <t>env.first_hazard_seen</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>codex.world.interior</t>
+          <t>codex.world.territories</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3441,71 +3441,112 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>codex.world.interior.title</t>
+          <t>codex.world.territories.title</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>codex.world.interior.body</t>
+          <t>codex.world.territories.body</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>codex.world.interior.hint</t>
+          <t>codex.world.territories.hint</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>codex.world.territories</t>
+          <t>codex.env.hazard,codex.world.interior</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>world.first_interior_entered,world.first_entrance_blocked</t>
+          <t>world.first_territory_entered,world.first_poi_found</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
+          <t>codex.world.interior</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>codex.world.interior.title</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>codex.world.interior.body</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>codex.world.interior.hint</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>codex.world.territories</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>world.first_interior_entered,world.first_entrance_blocked</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>codex.world.control</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>system</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
         <is>
           <t>codex.world.control.title</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>codex.world.control.body</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>codex.world.control.hint</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>codex.world.territories</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>world.first_outpost_destroyed,world.first_territory_pacified,world.first_territory_reclaimed</t>
         </is>
       </c>
-      <c r="I75" t="n">
+      <c r="I76" t="n">
         <v>341</v>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2734,7 +2734,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>codex.raid.director</t>
+          <t>codex.expedition.outpost</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2744,27 +2744,27 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>codex.raid.director.title</t>
+          <t>codex.expedition.outpost.title</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>codex.raid.director.body</t>
+          <t>codex.expedition.outpost.body</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>codex.raid.director.hint</t>
+          <t>codex.expedition.outpost.hint</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>codex.intel.raid_forecast,codex.signal.exposure,codex.defense.turret</t>
+          <t>codex.expedition.drop,codex.build.building</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>raid.first_planned,raid.first_warning</t>
+          <t>outpost.first_founded,outpost.first_panel_open,outpost.first_wiped</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -2775,7 +2775,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>codex.raid.siege</t>
+          <t>codex.raid.director</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2785,38 +2785,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>codex.raid.siege.title</t>
+          <t>codex.raid.director.title</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>codex.raid.siege.body</t>
+          <t>codex.raid.director.body</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>codex.raid.siege.hint</t>
+          <t>codex.raid.director.hint</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>codex.raid.director,codex.defense.barrier,codex.defense.turret</t>
+          <t>codex.intel.raid_forecast,codex.signal.exposure,codex.defense.turret</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>siege.first_unfold,siege.first_breach</t>
+          <t>raid.first_planned,raid.first_warning</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>codex.raid.hud</t>
+          <t>codex.raid.siege</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2826,38 +2826,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>codex.raid.hud.title</t>
+          <t>codex.raid.siege.title</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>codex.raid.hud.body</t>
+          <t>codex.raid.siege.body</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>codex.raid.hud.hint</t>
+          <t>codex.raid.siege.hint</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>codex.raid.director,codex.raid.siege,codex.defense.overview</t>
+          <t>codex.raid.director,codex.defense.barrier,codex.defense.turret</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>raid.hud_first_active,raid.first_spectate,raid.first_auto_pause</t>
+          <t>siege.first_unfold,siege.first_breach</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>codex.defense.overview</t>
+          <t>codex.raid.hud</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2867,38 +2867,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>codex.defense.overview.title</t>
+          <t>codex.raid.hud.title</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>codex.defense.overview.body</t>
+          <t>codex.raid.hud.body</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>codex.defense.overview.hint</t>
+          <t>codex.raid.hud.hint</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>codex.defense.turret,codex.raid.siege,codex.raid.hud</t>
+          <t>codex.raid.director,codex.raid.siege,codex.defense.overview</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>defense.overview_first_open,defense.first_weak_point</t>
+          <t>raid.hud_first_active,raid.first_spectate,raid.first_auto_pause</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>codex.raid.away</t>
+          <t>codex.defense.overview</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2908,38 +2908,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>codex.raid.away.title</t>
+          <t>codex.defense.overview.title</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>codex.raid.away.body</t>
+          <t>codex.defense.overview.body</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>codex.raid.away.hint</t>
+          <t>codex.defense.overview.hint</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>codex.raid.hud,codex.raid.director</t>
+          <t>codex.defense.turret,codex.raid.siege,codex.raid.hud</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>raid.away_first_alert,raid.away_first_choice</t>
+          <t>defense.overview_first_open,defense.first_weak_point</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>codex.raid.result</t>
+          <t>codex.raid.away</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2949,38 +2949,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>codex.raid.result.title</t>
+          <t>codex.raid.away.title</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>codex.raid.result.body</t>
+          <t>codex.raid.away.body</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>codex.raid.result.hint</t>
+          <t>codex.raid.away.hint</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>codex.raid.siege,codex.raid.director,codex.raid.away</t>
+          <t>codex.raid.hud,codex.raid.director</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>raid.first_result,raid.result_first_open</t>
+          <t>raid.away_first_alert,raid.away_first_choice</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>codex.raid.difficulty</t>
+          <t>codex.raid.result</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2990,38 +2990,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>codex.raid.difficulty.title</t>
+          <t>codex.raid.result.title</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>codex.raid.difficulty.body</t>
+          <t>codex.raid.result.body</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>codex.raid.difficulty.hint</t>
+          <t>codex.raid.result.hint</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>codex.raid.director,codex.raid.siege</t>
+          <t>codex.raid.siege,codex.raid.director,codex.raid.away</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>difficulty.first_open,difficulty.first_changed</t>
+          <t>raid.first_result,raid.result_first_open</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>codex.logistics.leak</t>
+          <t>codex.raid.difficulty</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3031,38 +3031,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>codex.logistics.leak.title</t>
+          <t>codex.raid.difficulty.title</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>codex.logistics.leak.body</t>
+          <t>codex.raid.difficulty.body</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>codex.logistics.leak.hint</t>
+          <t>codex.raid.difficulty.hint</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>codex.logistics.pipe,codex.logistics.fluid,codex.raid.siege</t>
+          <t>codex.raid.director,codex.raid.siege</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>logistics.leak.first,logistics.leak.first_react</t>
+          <t>difficulty.first_open,difficulty.first_changed</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>215</v>
+        <v>318</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>codex.env.daynight</t>
+          <t>codex.logistics.leak</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3072,38 +3072,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>codex.env.daynight.title</t>
+          <t>codex.logistics.leak.title</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>codex.env.daynight.body</t>
+          <t>codex.logistics.leak.body</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>codex.env.daynight.hint</t>
+          <t>codex.logistics.leak.hint</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>codex.economy.energy,codex.raid.director</t>
+          <t>codex.logistics.pipe,codex.logistics.fluid,codex.raid.siege</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>env.first_night,env.calendar_first_open</t>
+          <t>logistics.leak.first,logistics.leak.first_react</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>330</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>codex.env.silent_night</t>
+          <t>codex.env.daynight</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3113,38 +3113,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>codex.env.silent_night.title</t>
+          <t>codex.env.daynight.title</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>codex.env.silent_night.body</t>
+          <t>codex.env.daynight.body</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>codex.env.silent_night.hint</t>
+          <t>codex.env.daynight.hint</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>codex.env.daynight,codex.raid.director</t>
+          <t>codex.economy.energy,codex.raid.director</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>env.first_silent_warning,env.first_silent_night,env.first_storm_debris</t>
+          <t>env.first_night,env.calendar_first_open</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>codex.env.weather</t>
+          <t>codex.env.silent_night</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3154,38 +3154,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>codex.env.weather.title</t>
+          <t>codex.env.silent_night.title</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>codex.env.weather.body</t>
+          <t>codex.env.silent_night.body</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>codex.env.weather.hint</t>
+          <t>codex.env.silent_night.hint</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>codex.env.daynight,codex.env.roof,codex.intel.weather</t>
+          <t>codex.env.daynight,codex.raid.director</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>env.first_weather_warning,env.first_weather,env.first_pipe_frozen</t>
+          <t>env.first_silent_warning,env.first_silent_night,env.first_storm_debris</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>codex.env.roof</t>
+          <t>codex.env.weather</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3195,38 +3195,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>codex.env.roof.title</t>
+          <t>codex.env.weather.title</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>codex.env.roof.body</t>
+          <t>codex.env.weather.body</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>codex.env.roof.hint</t>
+          <t>codex.env.weather.hint</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>codex.env.weather</t>
+          <t>codex.env.daynight,codex.env.roof,codex.intel.weather</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>env.first_roof,env.first_weather</t>
+          <t>env.first_weather_warning,env.first_weather,env.first_pipe_frozen</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>codex.env.pollution</t>
+          <t>codex.env.roof</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3236,38 +3236,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>codex.env.pollution.title</t>
+          <t>codex.env.roof.title</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>codex.env.pollution.body</t>
+          <t>codex.env.roof.body</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>codex.env.pollution.hint</t>
+          <t>codex.env.roof.hint</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>codex.env.purification,codex.env.returned_area,codex.env.weather</t>
+          <t>codex.env.weather</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>env.first_pollution_seen,env.first_repollution</t>
+          <t>env.first_roof,env.first_weather</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>codex.env.purification</t>
+          <t>codex.env.pollution</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3277,38 +3277,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>codex.env.purification.title</t>
+          <t>codex.env.pollution.title</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>codex.env.purification.body</t>
+          <t>codex.env.pollution.body</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>codex.env.purification.hint</t>
+          <t>codex.env.pollution.hint</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>codex.env.pollution,codex.env.returned_area</t>
+          <t>codex.env.purification,codex.env.returned_area,codex.env.weather</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>env.first_purifier,env.first_purified</t>
+          <t>env.first_pollution_seen,env.first_repollution</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>codex.env.returned_area</t>
+          <t>codex.env.purification</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3318,38 +3318,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>codex.env.returned_area.title</t>
+          <t>codex.env.purification.title</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>codex.env.returned_area.body</t>
+          <t>codex.env.purification.body</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>codex.env.returned_area.hint</t>
+          <t>codex.env.purification.hint</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>codex.env.purification,codex.env.pollution</t>
+          <t>codex.env.pollution,codex.env.returned_area</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>env.first_purified,env.first_return_milestone</t>
+          <t>env.first_purifier,env.first_purified</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>codex.env.exploration</t>
+          <t>codex.env.returned_area</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3359,38 +3359,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>codex.env.exploration.title</t>
+          <t>codex.env.returned_area.title</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>codex.env.exploration.body</t>
+          <t>codex.env.returned_area.body</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>codex.env.exploration.hint</t>
+          <t>codex.env.returned_area.hint</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>codex.env.hazard,codex.env.returned_area</t>
+          <t>codex.env.purification,codex.env.pollution</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>env.first_fog_blocked,env.first_relic_found,env.first_relic_recovered</t>
+          <t>env.first_purified,env.first_return_milestone</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>codex.env.hazard</t>
+          <t>codex.env.exploration</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3400,38 +3400,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>codex.env.hazard.title</t>
+          <t>codex.env.exploration.title</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>codex.env.hazard.body</t>
+          <t>codex.env.exploration.body</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>codex.env.hazard.hint</t>
+          <t>codex.env.exploration.hint</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>codex.env.exploration</t>
+          <t>codex.env.hazard,codex.env.returned_area</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>env.first_hazard_seen</t>
+          <t>env.first_fog_blocked,env.first_relic_found,env.first_relic_recovered</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>codex.world.territories</t>
+          <t>codex.env.hazard</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3441,38 +3441,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>codex.world.territories.title</t>
+          <t>codex.env.hazard.title</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>codex.world.territories.body</t>
+          <t>codex.env.hazard.body</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>codex.world.territories.hint</t>
+          <t>codex.env.hazard.hint</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>codex.env.hazard,codex.world.interior</t>
+          <t>codex.env.exploration</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>world.first_territory_entered,world.first_poi_found</t>
+          <t>env.first_hazard_seen</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>codex.world.interior</t>
+          <t>codex.world.territories</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3482,71 +3482,112 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>codex.world.interior.title</t>
+          <t>codex.world.territories.title</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>codex.world.interior.body</t>
+          <t>codex.world.territories.body</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>codex.world.interior.hint</t>
+          <t>codex.world.territories.hint</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>codex.world.territories</t>
+          <t>codex.env.hazard,codex.world.interior</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>world.first_interior_entered,world.first_entrance_blocked</t>
+          <t>world.first_territory_entered,world.first_poi_found</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
+          <t>codex.world.interior</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>codex.world.interior.title</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>codex.world.interior.body</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>codex.world.interior.hint</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>codex.world.territories</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>world.first_interior_entered,world.first_entrance_blocked</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>codex.world.control</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>system</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
         <is>
           <t>codex.world.control.title</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>codex.world.control.body</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>codex.world.control.hint</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>codex.world.territories</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>world.first_outpost_destroyed,world.first_territory_pacified,world.first_territory_reclaimed</t>
         </is>
       </c>
-      <c r="I76" t="n">
+      <c r="I77" t="n">
         <v>341</v>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3591,6 +3591,47 @@
         <v>341</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>codex.expedition.protocol</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>codex.expedition.protocol.title</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>codex.expedition.protocol.body</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>codex.expedition.protocol.hint</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>codex.research.analysis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>loot.first_field_drop,loot.first_encrypted_rejected,signal.raw.first_encrypted</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>352</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3632,6 +3632,47 @@
         <v>352</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>codex.expedition.pick</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>codex.expedition.pick.title</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>codex.expedition.pick.body</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>codex.expedition.pick.hint</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>codex.expedition.protocol</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>loot.first_packet,loot.first_pick</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>353</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3673,6 +3673,47 @@
         <v>353</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>codex.expedition.cargo</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>codex.expedition.cargo.title</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>codex.expedition.cargo.body</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>codex.expedition.cargo.hint</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>codex.expedition.pick,codex.expedition.protocol</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>loot.first_cargo_open,loot.first_auto_pickup,loot.first_cargo_full</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>354</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3714,6 +3714,47 @@
         <v>354</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>codex.expedition.quests</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>codex.expedition.quests.title</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>codex.expedition.quests.body</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>codex.expedition.quests.hint</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>codex.world.control</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>quest.first_new,quest.first_log_open,quest.first_track</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>357</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3755,6 +3755,47 @@
         <v>357</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>codex.heritage</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>codex.heritage.title</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>codex.heritage.body</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>codex.heritage.hint</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>codex.env.exploration</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>heritage.first_found,heritage.first_delivered,heritage.vault_first_open</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>339</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3796,6 +3796,47 @@
         <v>339</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>codex.narrative</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>codex.narrative.title</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>codex.narrative.body</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>codex.narrative.hint</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>codex.heritage</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>narrative.first_entry,narrative.library_first_open</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>340</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>system</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>system</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>system</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>system</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>system</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>system</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3837,6 +3837,129 @@
         <v>340</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>codex.world.site_content</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>codex.world.site_content.title</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>codex.world.site_content.body</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>codex.world.site_content.hint</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>codex.world.control,codex.world.territories</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>act1.pace.first_expedition,site.first_garrison_destroyed</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>codex.world.signal_contacts</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>codex.world.signal_contacts.title</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>codex.world.signal_contacts.body</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>codex.world.signal_contacts.hint</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>codex.intel.listening_post,codex.world.site_content</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>site.first_contact_seen,site.first_contact_identified</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>codex.act1.pacing</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>codex.act1.pacing.title</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>codex.act1.pacing.body</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>codex.act1.pacing.hint</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>codex.narrative,codex.logistics.belt</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>act1.pace.wake,act1.pace.belts_open,act1.pace.act1_end</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>347</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3960,6 +3960,252 @@
         <v>347</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>codex.clarity.spray</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>codex.clarity.spray.title</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>codex.clarity.spray.body</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>codex.clarity.spray.hint</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>codex.clarity.acid,codex.clarity.chill</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>clarity.first_spray,clarity.first_pool_washed</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>codex.clarity.pivot</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>codex.clarity.pivot.title</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>codex.clarity.pivot.body</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>codex.clarity.pivot.hint</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>codex.clarity.spray</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>clarity.first_pivot,clarity.first_split</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>codex.clarity.crawler</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>codex.clarity.crawler.title</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>codex.clarity.crawler.body</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>codex.clarity.crawler.hint</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>codex.clarity.spray</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>clarity.first_burst,clarity.first_slick_ignite</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>codex.clarity.chill</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>codex.clarity.chill.title</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>codex.clarity.chill.body</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>codex.clarity.chill.hint</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>codex.clarity.spray</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>clarity.first_freeze</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>codex.clarity.air</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>codex.clarity.air.title</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>codex.clarity.air.body</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>codex.clarity.air.hint</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>codex.clarity.spray</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>clarity.first_drone</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>codex.clarity.acid</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>codex.clarity.acid.title</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>codex.clarity.acid.body</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>codex.clarity.acid.hint</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>codex.env.hazard,codex.clarity.spray</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>clarity.first_acid</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>366</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CodexEntry-机制图鉴条目.xlsx
@@ -4158,7 +4158,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>clarity.first_drone</t>
+          <t>clarity.first_air,clarity.first_drone</t>
         </is>
       </c>
       <c r="I91" t="n">
